--- a/artfynd/A 59451-2021 artfynd.xlsx
+++ b/artfynd/A 59451-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59451-2021 artfynd.xlsx
+++ b/artfynd/A 59451-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90907434</v>
+        <v>90907433</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697753.0018337648</v>
+        <v>697712</v>
       </c>
       <c r="R2" t="n">
-        <v>7416153.155017676</v>
+        <v>7416026</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -748,19 +743,9 @@
           <t>2019-09-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90907431</v>
+        <v>90907435</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697779.8849160373</v>
+        <v>697754</v>
       </c>
       <c r="R3" t="n">
-        <v>7415956.836515786</v>
+        <v>7416154</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -869,19 +849,9 @@
           <t>2019-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90907435</v>
+        <v>90907434</v>
       </c>
       <c r="B4" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697754.1270787701</v>
+        <v>697753</v>
       </c>
       <c r="R4" t="n">
-        <v>7416154.027886149</v>
+        <v>7416153</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -990,19 +955,9 @@
           <t>2019-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90907433</v>
+        <v>90907431</v>
       </c>
       <c r="B5" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1588</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697711.8970849625</v>
+        <v>697780</v>
       </c>
       <c r="R5" t="n">
-        <v>7416025.921617787</v>
+        <v>7415957</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1111,19 +1061,9 @@
           <t>2019-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,12 +1102,7 @@
         <v>90907432</v>
       </c>
       <c r="B6" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697761.105986364</v>
+        <v>697761</v>
       </c>
       <c r="R6" t="n">
-        <v>7415991.886429117</v>
+        <v>7415992</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1232,19 +1167,9 @@
           <t>2019-09-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 59451-2021 artfynd.xlsx
+++ b/artfynd/A 59451-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Statens Fastighetsverk - NVB - Greensway</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90907433</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Statens Fastighetsverk - NVB - Greensway</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90907435</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Statens Fastighetsverk - NVB - Greensway</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90907434</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Statens Fastighetsverk - NVB - Greensway</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90907431</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
           <t>Statens Fastighetsverk - NVB - Greensway</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90907432</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>